--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_012_Algeria.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_012_Algeria.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf86e04eb725b4cac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rce68e349ae7c495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb3a9818d3bbf4821"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R8154d04c00654dd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R42964b85536d4f04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb2ea200e3328477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R59945b09696144e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rc7dc2693812c4a04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rce51653b55dd4bff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R51609778a31f472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Ra562450a9c594df6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Radff239141864a07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ012CommercialTable" displayName="EEZ012CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ012CommercialTable" displayName="EEZ012CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ012FunctionalTable" displayName="EEZ012FunctionalTable" ref="A1:O27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O27"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ012FunctionalTable" displayName="EEZ012FunctionalTable" ref="A1:E27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E27"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ012ValidationTable" displayName="EEZ012ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ012ValidationTable" displayName="EEZ012ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -13223,7 +13177,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1df4696698a64afc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfef3ef06fc6a4962"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13233,20 +13187,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13254,714 +13198,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>10440.2019777161</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>10440.2019777161</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$188,A2,'Species'!$U$2:$U$188))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1344958.5517378533</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1344958.5517378533</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2346.3963411505</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.9481895835327423</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>887.5433687588542</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2346.3963411505</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1034.273532644761</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$188,A3,'Species'!$U$2:$U$188))</x:f>
-        <x:v>2426815.632746469</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.9481895835327423</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>887.5433687588542</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2082528.5130681645</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>344287.11967830476</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1653216834813322</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.16532168348133233</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>14231.7094574</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2235453819166517</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>167.31904685145736</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>14231.7094574</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>181.4163852759123</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$188,A4,'Species'!$U$2:$U$188))</x:f>
-        <x:v>2581865.286058523</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2235453819166517</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>167.31904685145736</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2381236.0614790395</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>200629.22457948374</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0842542357832714</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.08425423578327149</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>486.89431474660006</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.547428713201062</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>352.71888520624736</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>486.89431474660006</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>413.7113899306505</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$188,A5,'Species'!$U$2:$U$188))</x:f>
-        <x:v>201433.72370314752</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.547428713201062</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>352.71888520624736</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>171736.8199106805</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>29696.903792467027</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1729210067352607</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.17292100673526065</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>72162.08903470742</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.960119181780417</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>91.22611533614433</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>72162.08903470742</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>96.14473831990594</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$188,A6,'Species'!$U$2:$U$188))</x:f>
-        <x:v>6938005.1668596985</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.960119181780417</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>91.22611533614433</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>6583067.057177335</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>354938.10968236346</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0539168303466366</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.053916830346636725</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>181.6985737328</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.1181275067598584</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>13.125852111245381</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>181.6985737328</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>21.41399890029413</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$188,A7,'Species'!$U$2:$U$188))</x:f>
-        <x:v>3890.893058099191</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.1181275067598584</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>13.125852111245381</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2384.9486076409476</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1505.9444504582434</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.6314368559697545</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.6314368559697544</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>36809.37634451221</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.372264786214011</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>235.64855782673092</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>36809.37634451221</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>306.752228240694</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$188,A8,'Species'!$U$2:$U$188))</x:f>
-        <x:v>11291358.213829413</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.372264786214011</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>235.64855782673092</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>8674076.450085687</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2617281.7637437265</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.3017360728608602</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.30173607286086024</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>53735.6639720045</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.5230301224048044</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>333.44953982128783</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>53735.6639720045</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>464.0400230804298</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$188,A9,'Species'!$U$2:$U$188))</x:f>
-        <x:v>24935498.749811187</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.5230301224048044</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>333.44953982128783</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>17918132.423456255</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>7017366.326354932</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.3916349182222052</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.3916349182222051</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>339.5530731604</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.521682433526002</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>332.4163936145811</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>339.5530731604</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>346.59152463875927</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$188,A10,'Species'!$U$2:$U$188))</x:f>
-        <x:v>117686.2173224392</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.521682433526002</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>332.4163936145811</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>112873.00802072819</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4813.209301711016</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.042642695415959</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.04264269541595907</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>5302.6204981845995</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.838393249933915</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>689.2761475040745</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>5302.6204981845995</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>706.0195696931145</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$188,A11,'Species'!$U$2:$U$188))</x:f>
-        <x:v>3743753.8423741795</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.838393249933915</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>689.2761475040745</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3654969.828664817</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>88784.0137093626</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.024291312342186</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.02429131234218586</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>19304.209336284202</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.293021766940148</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1963.4586833744943</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>19304.209336284202</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2084.879607418633</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$188,A12,'Species'!$U$2:$U$188))</x:f>
-        <x:v>40246952.382559314</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.293021766940148</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1963.4586833744943</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>37903017.4470062</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>2343934.935553111</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0618403254788424</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.061840325478842544</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>21303.7434756212</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.435353842266774</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2724.9205381582938</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>21303.7434756212</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2798.795382913612</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$188,A13,'Species'!$U$2:$U$188))</x:f>
-        <x:v>59624818.878344595</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.435353842266774</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2724.9205381582938</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>58051008.136375956</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1573810.7419686392</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0271108253326346</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.027110825332634612</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bbec9dc01dd4cb6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cdefa55cdac46f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13971,20 +13451,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13992,1470 +13462,516 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4164.6711134428</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8637307622673953</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>730.6859595504111</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4164.6711134428</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>816.4410528997669</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$188,A2,'Species'!$U$2:$U$188))</x:f>
-        <x:v>3400208.4688404836</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8637307622673953</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>730.6859595504111</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3043066.708737831</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>357141.7601026525</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1173624485710942</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.11736244857109417</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>387.3560387274</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.0461213380044745</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1112.0423786044823</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>387.3560387274</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1402.801913297337</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$188,A3,'Species'!$U$2:$U$188))</x:f>
-        <x:v>543383.7922540741</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.0461213380044745</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1112.0423786044823</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>430756.3306732279</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>112627.46158084623</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2614644372256145</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.26146443722561447</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>44.7827489286</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.9199999999999995</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>831.76377110267</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>44.7827489286</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$188,A4,'Species'!$U$2:$U$188))</x:f>
-        <x:v>37248.66812919643</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.9199999999999995</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>831.76377110267</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>37248.66812919639</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>3.637978807091713e-11</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>9.766735268153598e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>982.610168346</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.8891813717116475</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>774.7852990273116</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>982.610168346</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>818.080396450624</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$188,A5,'Species'!$U$2:$U$188))</x:f>
-        <x:v>803854.11607691</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.8891813717116475</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>774.7852990273116</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>761311.9131092326</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>42542.2029676775</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0558801225031842</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.055880122503184276</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>317.29725537110005</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.326806273744244</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2122.2975550289716</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>317.29725537110005</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2219.7235042384523</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$188,A6,'Species'!$U$2:$U$188))</x:f>
-        <x:v>704312.1755775813</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.326806273744244</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2122.2975550289716</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>673399.1892914888</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>30912.986286092433</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0459058858069272</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.04590588580692719</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>15044.2589449756</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.446637762632347</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2796.647712027376</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>15044.2589449756</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2842.7996527586756</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$188,A7,'Species'!$U$2:$U$188))</x:f>
-        <x:v>42767814.10478824</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.446637762632347</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2796.647712027376</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>42073492.3576134</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>694321.7471748367</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0165025936348067</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.01650259363480664</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>457.92396788599996</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.698998316471094</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>500.0325966125802</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>457.92396788599996</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>513.0830503421582</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$188,A8,'Species'!$U$2:$U$188))</x:f>
-        <x:v>234953.02626773337</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.698998316471094</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>500.0325966125802</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>228976.91071317234</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>5976.115554561024</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.026099205967745</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.026099205967744923</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>5058.831743205699</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.901866548232633</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>797.7495138993187</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>5058.831743205699</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>859.2298118686181</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$188,A9,'Species'!$U$2:$U$188))</x:f>
-        <x:v>4346699.046989626</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.901866548232633</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>797.7495138993187</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>4035680.5640407894</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>311018.48294883687</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0770671707072437</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.07706717070724366</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>17553.656152676303</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.322039892164347</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2099.132690817653</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>17553.656152676303</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2181.3754863072927</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$188,A10,'Species'!$U$2:$U$188))</x:f>
-        <x:v>38291115.22651527</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.322039892164347</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2099.132690817653</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>36847453.47345526</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1443661.753060013</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0391794172180724</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03917941721807236</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>4282.3745430714</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.104963353192394</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>127.33956243131118</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>4282.3745430714</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>156.68393807109217</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$188,A11,'Species'!$U$2:$U$188))</x:f>
-        <x:v>670979.3077038209</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.104963353192394</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>127.33956243131118</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>545315.7004816981</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>125663.60722212272</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2304419386992145</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.23044193869921453</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>707.3598885986</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.628094706513762</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>424.7121707495922</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>707.3598885986</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>696.5643704227423</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$188,A12,'Species'!$U$2:$U$188))</x:f>
-        <x:v>492721.695463985</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.628094706513762</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>424.7121707495922</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>300424.3537879011</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>192297.34167608386</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.6400857295738591</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.6400857295738591</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.20856951010000002</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.20856951010000002</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$188,A13,'Species'!$U$2:$U$188))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>250.75570413880737</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>250.75570413880737</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>13378.3937935377</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.485689026501648</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>305.9771721160266</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>13378.3937935377</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>506.83387833580093</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$188,A14,'Species'!$U$2:$U$188))</x:f>
-        <x:v>6780623.2122823205</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.485689026501648</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>305.9771721160266</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>4093483.100401267</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2687140.1118810535</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.6564434360600253</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.6564434360600254</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>43913.11855583031</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.292371639458809</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>196.05216359657223</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>43913.11855583031</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>225.41981672488885</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$188,A15,'Species'!$U$2:$U$188))</x:f>
-        <x:v>9898887.136673585</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.292371639458809</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>196.05216359657223</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>8609261.903143317</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1289625.233530268</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.149795098353253</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.1497950983532531</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>25909.290716187203</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.8430540816489094</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>696.713268739241</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>25909.290716187203</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>1066.0011955523362</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$188,A16,'Species'!$U$2:$U$188))</x:f>
-        <x:v>27619334.879368603</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.8430540816489094</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>696.713268739241</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>18051346.625590056</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>9567988.253778547</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.5300429077249404</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.5300429077249406</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>8596.5283490311</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.6317176730360368</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>428.27001931287066</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>8596.5283490311</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>503.80375883907146</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$188,A17,'Species'!$U$2:$U$188))</x:f>
-        <x:v>4330963.295208505</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.6317176730360368</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>428.27001931287066</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>3681635.362063189</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>649327.9331453163</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.1763694307796502</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.17636943077965028</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>181.6985737328</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.1181275067598584</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>13.125852111245381</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>181.6985737328</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>21.41399890029413</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$188,A18,'Species'!$U$2:$U$188))</x:f>
-        <x:v>3890.893058099191</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.1181275067598584</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>13.125852111245381</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>2384.9486076409476</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>1505.9444504582434</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.6314368559697545</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.6314368559697544</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>9949.3349143286</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.274585241912036</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>188.18510335880418</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>9949.3349143286</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>192.0616799825209</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$188,A19,'Species'!$U$2:$U$188))</x:f>
-        <x:v>1910885.9783547015</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.274585241912036</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>188.18510335880418</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1872316.6192042867</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>38569.35915041482</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0205998060129415</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.020599806012941528</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small bathypelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>15.6894517979</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.01</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>102.32929922807536</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>15.6894517979</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$188,A20,'Species'!$U$2:$U$188))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1605.490607751774</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.01</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>1605.490607751774</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>67.23296556700001</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.564861264747191</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>367.1649910064365</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>67.23296556700001</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>379.6899845841642</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$188,A21,'Species'!$U$2:$U$188))</x:f>
-        <x:v>25527.683659681876</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.564861264747191</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>367.1649910064365</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>24685.59119774361</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>842.092461938264</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0341127119538152</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.03411271195381521</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>819.4430021898002</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.4433484760528494</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>277.554629798218</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>819.4430021898002</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>360.94983470988814</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$188,A22,'Species'!$U$2:$U$188))</x:f>
-        <x:v>295777.81619458285</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.4433484760528494</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>277.554629798218</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>227440.19911353034</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>68337.6170810525</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.3004641103349577</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.3004641103349576</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>82833.90676986871</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>2.9797614629016382</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>95.44681984888959</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>82833.90676986871</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>100.47134359670855</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$188,A23,'Species'!$U$2:$U$188))</x:f>
-        <x:v>8322433.908533202</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>2.9797614629016382</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>95.44681984888959</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>7906232.976843375</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>416200.9316898268</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0526421284205565</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.05264212842055639</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>198.6646419413</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.306146475120287</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>202.37016003206742</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>198.6646419413</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>257.96742778471844</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$188,A24,'Species'!$U$2:$U$188))</x:f>
-        <x:v>51249.00667336925</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.306146475120287</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>202.37016003206742</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>40203.79538237426</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>11045.211290994994</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.2747305617776903</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.2747305617776904</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>486.89431474660006</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.547428713201062</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>352.71888520624736</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>486.89431474660006</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>413.7113899306505</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$188,A25,'Species'!$U$2:$U$188))</x:f>
-        <x:v>201433.72370314752</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.547428713201062</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>352.71888520624736</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>171736.8199106805</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>29696.903792467027</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.1729210067352607</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.17292100673526065</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>57.9601788531</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.7237103823195934</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>529.3103453216124</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>57.9601788531</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>584.8229638515957</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$188,A26,'Species'!$U$2:$U$188))</x:f>
-        <x:v>33896.44358223852</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.7237103823195934</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>529.3103453216124</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>30678.922283636777</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>3217.521298601743</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.1048772596656002</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.10487725966560021</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="18" customHeight="1">
       <x:c r="A27" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B27" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D27" s="31" t="n">
+      <x:c r="B27" s="31" t="n">
         <x:v>1234.6690368688</x:v>
       </x:c>
+      <x:c r="C27" s="32" t="n">
+        <x:v>4.12750435203252</x:v>
+      </x:c>
+      <x:c r="D27" s="32" t="n">
+        <x:f>IF(C27="","",(1/'Metadata'!$B$5)^(C27-1))</x:f>
+        <x:v>1341.233375737368</x:v>
+      </x:c>
       <x:c r="E27" s="31" t="n">
-        <x:v>1234.6690368688</x:v>
-      </x:c>
-      <x:c r="F27" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="32" t="n">
-        <x:f>IF(E27=0,"",I27/E27)</x:f>
-        <x:v>1366.3480947674645</x:v>
-      </x:c>
-      <x:c r="I27" s="31" t="n">
-        <x:f>IF(C27=0,"",SUMIF('Species'!$G$2:$G$188,A27,'Species'!$U$2:$U$188))</x:f>
-        <x:v>1686987.6861940653</x:v>
-      </x:c>
-      <x:c r="J27" s="32" t="n">
-        <x:v>4.12750435203252</x:v>
-      </x:c>
-      <x:c r="K27" s="32" t="n">
-        <x:f>IF(J27="","",(1/'Metadata'!$B$5)^(J27-1))</x:f>
-        <x:v>1341.233375737368</x:v>
-      </x:c>
-      <x:c r="L27" s="31" t="n">
-        <x:f>IF(E27=0,"",E27*K27)</x:f>
+        <x:f>IF(B27=0,"",B27*D27)</x:f>
         <x:v>1655979.3202379458</x:v>
       </x:c>
-      <x:c r="M27" s="31" t="n">
-        <x:f>IF(E27=0,"",I27-L27)</x:f>
-        <x:v>31008.365956119495</x:v>
-      </x:c>
-      <x:c r="N27" s="32" t="n">
-        <x:f>IF(L27=0,"",I27/L27)</x:f>
-        <x:v>1.0187250925039715</x:v>
-      </x:c>
-      <x:c r="O27" s="34" t="n">
-        <x:f>IF(L27=0,"",M27/L27)</x:f>
-        <x:v>0.01872509250397157</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G27">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O27">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25da41bd52484d67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51bf52fe09de49ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15630,7 +14146,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -15729,7 +14245,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>153457037.53840494</x:v>
+        <x:v>138879989.24559036</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15743,7 +14259,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>153457037.5384049</x:v>
+        <x:v>135346368.60032412</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15757,7 +14273,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-14577048.292814553</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15771,7 +14287,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-18110668.938080788</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15782,9 +14298,9 @@
         <x:v>EEZ_012</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -15796,47 +14312,19 @@
         <x:v>EEZ_012</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_012</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_012</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6eb642b7b8764787"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3387be1070684463"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15883,7 +14371,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
